--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,55 +528,85 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -679,7 +709,25 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -780,7 +828,25 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -881,7 +947,25 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -982,7 +1066,25 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -1083,7 +1185,25 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -1184,7 +1304,25 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -1285,7 +1423,25 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>
@@ -1386,7 +1542,25 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>45974.5</v>
       </c>
     </row>

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-13.xlsx
+++ b/jogos_2025-11-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
